--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,228 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120288114</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Känne, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>508506</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6886533</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120288115</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Känne, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508416</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6886540</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288114</v>
+        <v>120288115</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508506</v>
+        <v>508416</v>
       </c>
       <c r="R4" t="n">
-        <v>6886533</v>
+        <v>6886540</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288115</v>
+        <v>120288114</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,25 +1040,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508416</v>
+        <v>508506</v>
       </c>
       <c r="R5" t="n">
-        <v>6886540</v>
+        <v>6886533</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288115</v>
+        <v>120288114</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508416</v>
+        <v>508506</v>
       </c>
       <c r="R4" t="n">
-        <v>6886540</v>
+        <v>6886533</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288114</v>
+        <v>120288115</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,25 +1040,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508506</v>
+        <v>508416</v>
       </c>
       <c r="R5" t="n">
-        <v>6886533</v>
+        <v>6886540</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288114</v>
+        <v>120288115</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508506</v>
+        <v>508416</v>
       </c>
       <c r="R4" t="n">
-        <v>6886533</v>
+        <v>6886540</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288115</v>
+        <v>120288114</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,25 +1040,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508416</v>
+        <v>508506</v>
       </c>
       <c r="R5" t="n">
-        <v>6886540</v>
+        <v>6886533</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>121152617</v>
       </c>
       <c r="B6" t="n">
-        <v>57230</v>
+        <v>57233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>121152617</v>
       </c>
       <c r="B6" t="n">
-        <v>57233</v>
+        <v>57236</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -1142,11 +1142,11 @@
         <v>121152617</v>
       </c>
       <c r="B6" t="n">
-        <v>57236</v>
+        <v>57358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>121152617</v>
       </c>
       <c r="B6" t="n">
-        <v>57358</v>
+        <v>57361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97909274</v>
+        <v>120288115</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508505.3282650937</v>
+        <v>508416</v>
       </c>
       <c r="R2" t="n">
-        <v>6886533.598119223</v>
+        <v>6886540</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +747,9 @@
           <t>2021-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97909275</v>
+        <v>121152617</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100011</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508415.3007028527</v>
+        <v>508274</v>
       </c>
       <c r="R3" t="n">
-        <v>6886540.394696647</v>
+        <v>6886540</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288115</v>
+        <v>120288114</v>
       </c>
       <c r="B4" t="n">
-        <v>91931</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508416</v>
+        <v>508506</v>
       </c>
       <c r="R4" t="n">
-        <v>6886540</v>
+        <v>6886533</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1025,228 +990,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>120288114</v>
-      </c>
-      <c r="B5" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Känne, Hls</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>508506</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6886533</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ytterhogdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2021-10-11</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2021-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>121152617</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57361</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100011</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kungsörn</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Aquila chrysaetos</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Känne, Hls</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>508274</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6886540</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ytterhogdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42826-2021 artfynd.xlsx
+++ b/artfynd/A 42826-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288115</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152617</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288114</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>